--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.44880343368835</v>
+        <v>7.872930557974357</v>
       </c>
       <c r="D2" t="n">
-        <v>20.86264604502507</v>
+        <v>3.390179982316573</v>
       </c>
       <c r="E2" t="n">
-        <v>15.03749147376732</v>
+        <v>2.44359236448719</v>
       </c>
       <c r="F2" t="n">
-        <v>7.530735965340805</v>
+        <v>1.223744594367881</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.39200203152232</v>
+        <v>5.588700330122378</v>
       </c>
       <c r="D3" t="n">
-        <v>17.81719670308281</v>
+        <v>2.895294464250956</v>
       </c>
       <c r="E3" t="n">
-        <v>15.03749147376732</v>
+        <v>2.44359236448719</v>
       </c>
       <c r="F3" t="n">
-        <v>7.530735965340805</v>
+        <v>1.223744594367881</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.76619623367858</v>
+        <v>9.387006887972769</v>
       </c>
       <c r="D4" t="n">
-        <v>36.09295668384138</v>
+        <v>5.865105461124224</v>
       </c>
       <c r="E4" t="n">
-        <v>15.03749147376732</v>
+        <v>2.44359236448719</v>
       </c>
       <c r="F4" t="n">
-        <v>7.530735965340805</v>
+        <v>1.223744594367881</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.94186321870734</v>
+        <v>2.915552773039942</v>
       </c>
       <c r="D5" t="n">
-        <v>18.08310726974037</v>
+        <v>2.93850493133281</v>
       </c>
       <c r="E5" t="n">
-        <v>15.03749147376732</v>
+        <v>2.44359236448719</v>
       </c>
       <c r="F5" t="n">
-        <v>7.530735965340805</v>
+        <v>1.223744594367881</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
